--- a/artfynd/A 5086-2022 artfynd.xlsx
+++ b/artfynd/A 5086-2022 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119867760</v>
+        <v>119867759</v>
       </c>
       <c r="B2" t="n">
         <v>57679</v>
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>584543</v>
+        <v>584544</v>
       </c>
       <c r="R2" t="n">
-        <v>6342900</v>
+        <v>6342921</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -795,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119868213</v>
+        <v>119867770</v>
       </c>
       <c r="B3" t="n">
-        <v>57851</v>
+        <v>57679</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,16 +811,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102990</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -833,19 +833,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Stor-Fänet, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>584530</v>
+        <v>584573</v>
       </c>
       <c r="R3" t="n">
-        <v>6342888</v>
+        <v>6343010</v>
       </c>
       <c r="S3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -869,22 +874,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,7 +909,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Angelia Ellvin</t>
+          <t>Engla Grönvall</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -915,10 +920,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119867759</v>
+        <v>119868213</v>
       </c>
       <c r="B4" t="n">
-        <v>57679</v>
+        <v>57851</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -931,16 +936,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>102990</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -959,13 +964,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>584544</v>
+        <v>584530</v>
       </c>
       <c r="R4" t="n">
-        <v>6342921</v>
+        <v>6342888</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -994,7 +999,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1004,7 +1009,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1035,7 +1040,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119867770</v>
+        <v>119867761</v>
       </c>
       <c r="B5" t="n">
         <v>57679</v>
@@ -1073,21 +1078,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Stor-Fänet, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>584573</v>
+        <v>584543</v>
       </c>
       <c r="R5" t="n">
-        <v>6343010</v>
+        <v>6342904</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1114,22 +1114,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Engla Grönvall</t>
+          <t>Angelia Ellvin</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1160,7 +1160,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119867761</v>
+        <v>119867760</v>
       </c>
       <c r="B6" t="n">
         <v>57679</v>
@@ -1207,7 +1207,7 @@
         <v>584543</v>
       </c>
       <c r="R6" t="n">
-        <v>6342904</v>
+        <v>6342900</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1249,7 +1249,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 5086-2022 artfynd.xlsx
+++ b/artfynd/A 5086-2022 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119867759</v>
+        <v>119867761</v>
       </c>
       <c r="B2" t="n">
         <v>57679</v>
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>584544</v>
+        <v>584543</v>
       </c>
       <c r="R2" t="n">
-        <v>6342921</v>
+        <v>6342904</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,7 +795,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119867770</v>
+        <v>119867759</v>
       </c>
       <c r="B3" t="n">
         <v>57679</v>
@@ -833,21 +833,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Stor-Fänet, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>584573</v>
+        <v>584544</v>
       </c>
       <c r="R3" t="n">
-        <v>6343010</v>
+        <v>6342921</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -874,22 +869,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,7 +904,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Engla Grönvall</t>
+          <t>Angelia Ellvin</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -920,10 +915,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119868213</v>
+        <v>119867770</v>
       </c>
       <c r="B4" t="n">
-        <v>57851</v>
+        <v>57679</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -936,16 +931,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102990</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -958,19 +953,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Stor-Fänet, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>584530</v>
+        <v>584573</v>
       </c>
       <c r="R4" t="n">
-        <v>6342888</v>
+        <v>6343010</v>
       </c>
       <c r="S4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -994,22 +994,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Angelia Ellvin</t>
+          <t>Engla Grönvall</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1040,7 +1040,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119867761</v>
+        <v>119867760</v>
       </c>
       <c r="B5" t="n">
         <v>57679</v>
@@ -1087,7 +1087,7 @@
         <v>584543</v>
       </c>
       <c r="R5" t="n">
-        <v>6342904</v>
+        <v>6342900</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1119,7 +1119,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1129,7 +1129,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1160,10 +1160,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119867760</v>
+        <v>119868213</v>
       </c>
       <c r="B6" t="n">
-        <v>57679</v>
+        <v>57851</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1176,16 +1176,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>102990</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1204,13 +1204,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>584543</v>
+        <v>584530</v>
       </c>
       <c r="R6" t="n">
-        <v>6342900</v>
+        <v>6342888</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1249,7 +1249,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 5086-2022 artfynd.xlsx
+++ b/artfynd/A 5086-2022 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119867761</v>
+        <v>119867770</v>
       </c>
       <c r="B2" t="n">
         <v>57679</v>
@@ -713,16 +713,21 @@
           <t>1</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Stor-Fänet, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>584543</v>
+        <v>584573</v>
       </c>
       <c r="R2" t="n">
-        <v>6342904</v>
+        <v>6343010</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -749,22 +754,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,7 +789,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Angelia Ellvin</t>
+          <t>Engla Grönvall</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -795,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119867759</v>
+        <v>119868213</v>
       </c>
       <c r="B3" t="n">
-        <v>57679</v>
+        <v>57851</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,16 +816,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>102990</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -839,13 +844,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>584544</v>
+        <v>584530</v>
       </c>
       <c r="R3" t="n">
-        <v>6342921</v>
+        <v>6342888</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -874,7 +879,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -884,7 +889,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,7 +920,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119867770</v>
+        <v>119867761</v>
       </c>
       <c r="B4" t="n">
         <v>57679</v>
@@ -953,21 +958,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Stor-Fänet, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>584573</v>
+        <v>584543</v>
       </c>
       <c r="R4" t="n">
-        <v>6343010</v>
+        <v>6342904</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -994,22 +994,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Engla Grönvall</t>
+          <t>Angelia Ellvin</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1160,10 +1160,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119868213</v>
+        <v>119867759</v>
       </c>
       <c r="B6" t="n">
-        <v>57851</v>
+        <v>57679</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1176,16 +1176,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102990</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1204,13 +1204,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>584530</v>
+        <v>584544</v>
       </c>
       <c r="R6" t="n">
-        <v>6342888</v>
+        <v>6342921</v>
       </c>
       <c r="S6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1249,7 +1249,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 5086-2022 artfynd.xlsx
+++ b/artfynd/A 5086-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119867770</v>
+        <v>119867760</v>
       </c>
       <c r="B2" t="n">
-        <v>57679</v>
+        <v>57689</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -713,21 +713,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Stor-Fänet, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>584573</v>
+        <v>584543</v>
       </c>
       <c r="R2" t="n">
-        <v>6343010</v>
+        <v>6342900</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -754,22 +749,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,7 +784,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Engla Grönvall</t>
+          <t>Angelia Ellvin</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -800,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119868213</v>
+        <v>119867770</v>
       </c>
       <c r="B3" t="n">
-        <v>57851</v>
+        <v>57689</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -816,16 +811,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102990</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -838,19 +833,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Stor-Fänet, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>584530</v>
+        <v>584573</v>
       </c>
       <c r="R3" t="n">
-        <v>6342888</v>
+        <v>6343010</v>
       </c>
       <c r="S3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -874,22 +874,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,7 +909,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Angelia Ellvin</t>
+          <t>Engla Grönvall</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -920,10 +920,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119867761</v>
+        <v>119868213</v>
       </c>
       <c r="B4" t="n">
-        <v>57679</v>
+        <v>57861</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -936,16 +936,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>102990</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -964,13 +964,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>584543</v>
+        <v>584530</v>
       </c>
       <c r="R4" t="n">
-        <v>6342904</v>
+        <v>6342888</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1040,10 +1040,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119867760</v>
+        <v>119867761</v>
       </c>
       <c r="B5" t="n">
-        <v>57679</v>
+        <v>57689</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
         <v>584543</v>
       </c>
       <c r="R5" t="n">
-        <v>6342900</v>
+        <v>6342904</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1119,7 +1119,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1129,7 +1129,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1163,7 +1163,7 @@
         <v>119867759</v>
       </c>
       <c r="B6" t="n">
-        <v>57679</v>
+        <v>57689</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 5086-2022 artfynd.xlsx
+++ b/artfynd/A 5086-2022 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119867760</v>
+        <v>119867761</v>
       </c>
       <c r="B2" t="n">
         <v>57689</v>
@@ -722,7 +722,7 @@
         <v>584543</v>
       </c>
       <c r="R2" t="n">
-        <v>6342900</v>
+        <v>6342904</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119867770</v>
+        <v>119868213</v>
       </c>
       <c r="B3" t="n">
-        <v>57689</v>
+        <v>57861</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,16 +811,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>102990</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -833,24 +833,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Stor-Fänet, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>584573</v>
+        <v>584530</v>
       </c>
       <c r="R3" t="n">
-        <v>6343010</v>
+        <v>6342888</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -874,22 +869,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,7 +904,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Engla Grönvall</t>
+          <t>Angelia Ellvin</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -920,10 +915,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119868213</v>
+        <v>119867770</v>
       </c>
       <c r="B4" t="n">
-        <v>57861</v>
+        <v>57689</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -936,16 +931,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102990</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -958,19 +953,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Stor-Fänet, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>584530</v>
+        <v>584573</v>
       </c>
       <c r="R4" t="n">
-        <v>6342888</v>
+        <v>6343010</v>
       </c>
       <c r="S4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -994,22 +994,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Angelia Ellvin</t>
+          <t>Engla Grönvall</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1040,7 +1040,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119867761</v>
+        <v>119867759</v>
       </c>
       <c r="B5" t="n">
         <v>57689</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>584543</v>
+        <v>584544</v>
       </c>
       <c r="R5" t="n">
-        <v>6342904</v>
+        <v>6342921</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1119,7 +1119,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1129,7 +1129,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1160,7 +1160,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119867759</v>
+        <v>119867760</v>
       </c>
       <c r="B6" t="n">
         <v>57689</v>
@@ -1204,10 +1204,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>584544</v>
+        <v>584543</v>
       </c>
       <c r="R6" t="n">
-        <v>6342921</v>
+        <v>6342900</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>

--- a/artfynd/A 5086-2022 artfynd.xlsx
+++ b/artfynd/A 5086-2022 artfynd.xlsx
@@ -915,7 +915,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119867770</v>
+        <v>119867760</v>
       </c>
       <c r="B4" t="n">
         <v>57689</v>
@@ -953,21 +953,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Stor-Fänet, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>584573</v>
+        <v>584543</v>
       </c>
       <c r="R4" t="n">
-        <v>6343010</v>
+        <v>6342900</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -994,22 +989,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1029,7 +1024,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Engla Grönvall</t>
+          <t>Angelia Ellvin</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1160,7 +1155,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119867760</v>
+        <v>119867770</v>
       </c>
       <c r="B6" t="n">
         <v>57689</v>
@@ -1198,16 +1193,21 @@
           <t>1</t>
         </is>
       </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Stor-Fänet, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>584543</v>
+        <v>584573</v>
       </c>
       <c r="R6" t="n">
-        <v>6342900</v>
+        <v>6343010</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1234,22 +1234,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1269,7 +1269,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Angelia Ellvin</t>
+          <t>Engla Grönvall</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">

--- a/artfynd/A 5086-2022 artfynd.xlsx
+++ b/artfynd/A 5086-2022 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119867761</v>
+        <v>119867770</v>
       </c>
       <c r="B2" t="n">
         <v>57689</v>
@@ -713,16 +713,21 @@
           <t>1</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Stor-Fänet, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>584543</v>
+        <v>584573</v>
       </c>
       <c r="R2" t="n">
-        <v>6342904</v>
+        <v>6343010</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -749,22 +754,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,7 +789,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Angelia Ellvin</t>
+          <t>Engla Grönvall</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -915,7 +920,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119867760</v>
+        <v>119867761</v>
       </c>
       <c r="B4" t="n">
         <v>57689</v>
@@ -962,7 +967,7 @@
         <v>584543</v>
       </c>
       <c r="R4" t="n">
-        <v>6342900</v>
+        <v>6342904</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -994,7 +999,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1004,7 +1009,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1155,7 +1160,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119867770</v>
+        <v>119867760</v>
       </c>
       <c r="B6" t="n">
         <v>57689</v>
@@ -1193,21 +1198,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Stor-Fänet, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>584573</v>
+        <v>584543</v>
       </c>
       <c r="R6" t="n">
-        <v>6343010</v>
+        <v>6342900</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1234,22 +1234,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1269,7 +1269,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Engla Grönvall</t>
+          <t>Angelia Ellvin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">

--- a/artfynd/A 5086-2022 artfynd.xlsx
+++ b/artfynd/A 5086-2022 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119867770</v>
+        <v>119867761</v>
       </c>
       <c r="B2" t="n">
         <v>57689</v>
@@ -713,21 +713,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Stor-Fänet, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>584573</v>
+        <v>584543</v>
       </c>
       <c r="R2" t="n">
-        <v>6343010</v>
+        <v>6342904</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -754,22 +749,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,7 +784,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Engla Grönvall</t>
+          <t>Angelia Ellvin</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -800,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119868213</v>
+        <v>119867770</v>
       </c>
       <c r="B3" t="n">
-        <v>57861</v>
+        <v>57689</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -816,16 +811,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102990</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -838,19 +833,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Stor-Fänet, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>584530</v>
+        <v>584573</v>
       </c>
       <c r="R3" t="n">
-        <v>6342888</v>
+        <v>6343010</v>
       </c>
       <c r="S3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -874,22 +874,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,7 +909,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Angelia Ellvin</t>
+          <t>Engla Grönvall</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -920,7 +920,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119867761</v>
+        <v>119867759</v>
       </c>
       <c r="B4" t="n">
         <v>57689</v>
@@ -964,10 +964,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>584543</v>
+        <v>584544</v>
       </c>
       <c r="R4" t="n">
-        <v>6342904</v>
+        <v>6342921</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -999,7 +999,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1040,7 +1040,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119867759</v>
+        <v>119867760</v>
       </c>
       <c r="B5" t="n">
         <v>57689</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>584544</v>
+        <v>584543</v>
       </c>
       <c r="R5" t="n">
-        <v>6342921</v>
+        <v>6342900</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119867760</v>
+        <v>119868213</v>
       </c>
       <c r="B6" t="n">
-        <v>57689</v>
+        <v>57861</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1176,16 +1176,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>102990</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1204,13 +1204,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>584543</v>
+        <v>584530</v>
       </c>
       <c r="R6" t="n">
-        <v>6342900</v>
+        <v>6342888</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1249,7 +1249,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 5086-2022 artfynd.xlsx
+++ b/artfynd/A 5086-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,27 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119867761</v>
+        <v>119868213</v>
       </c>
       <c r="B2" t="n">
-        <v>57689</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58497</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>102990</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -719,13 +714,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>584543</v>
+        <v>584530</v>
       </c>
       <c r="R2" t="n">
-        <v>6342904</v>
+        <v>6342888</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,7 +749,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +759,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,15 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119867770</v>
+        <v>119867759</v>
       </c>
       <c r="B3" t="n">
-        <v>57689</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -833,21 +823,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Stor-Fänet, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>584573</v>
+        <v>584544</v>
       </c>
       <c r="R3" t="n">
-        <v>6343010</v>
+        <v>6342921</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -874,22 +859,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,7 +894,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Engla Grönvall</t>
+          <t>Angelia Ellvin</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -920,15 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119867759</v>
+        <v>119867760</v>
       </c>
       <c r="B4" t="n">
-        <v>57689</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -964,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>584544</v>
+        <v>584543</v>
       </c>
       <c r="R4" t="n">
-        <v>6342921</v>
+        <v>6342900</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -1040,15 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119867760</v>
+        <v>119867761</v>
       </c>
       <c r="B5" t="n">
-        <v>57689</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1087,7 +1062,7 @@
         <v>584543</v>
       </c>
       <c r="R5" t="n">
-        <v>6342900</v>
+        <v>6342904</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1119,7 +1094,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1129,7 +1104,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1160,15 +1135,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119868213</v>
+        <v>119867770</v>
       </c>
       <c r="B6" t="n">
-        <v>57861</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1176,16 +1146,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102990</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1198,19 +1168,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Stor-Fänet, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>584530</v>
+        <v>584573</v>
       </c>
       <c r="R6" t="n">
-        <v>6342888</v>
+        <v>6343010</v>
       </c>
       <c r="S6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1234,22 +1209,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1269,10 +1244,135 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
+          <t>Engla Grönvall</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Alight - Oskarshamn</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>119867785</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Stor-Fänet, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>584539</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6343014</v>
+      </c>
+      <c r="S7" t="n">
+        <v>6</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Döderhult</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-04-10</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-04-10</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
           <t>Angelia Ellvin</t>
         </is>
       </c>
-      <c r="AY6" t="inlineStr">
+      <c r="AY7" t="inlineStr">
         <is>
           <t>Alight - Oskarshamn</t>
         </is>

--- a/artfynd/A 5086-2022 artfynd.xlsx
+++ b/artfynd/A 5086-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -787,6 +792,11 @@
           <t>Alight - Oskarshamn</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119868213</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -902,6 +912,11 @@
           <t>Alight - Oskarshamn</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119867759</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1017,6 +1032,11 @@
           <t>Alight - Oskarshamn</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119867760</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1132,6 +1152,11 @@
           <t>Alight - Oskarshamn</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119867761</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1252,6 +1277,11 @@
           <t>Alight - Oskarshamn</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119867770</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1377,8 +1407,21 @@
           <t>Alight - Oskarshamn</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119867785</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>